--- a/assessment/templates/security-admin-checklist.xlsx
+++ b/assessment/templates/security-admin-checklist.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Web Search Status: Verify the current web search setting in M365 Admin Center matches the intended governance level; Group Scoping: If using group-based web search, verify that only intended users can access web search functionality in Copilot; User Experience Test (Disabled): As a user with web search disabled, ask Copilot a question that would require web data — confirm no web results appear and response is based solely on M365 data; User Experience Test (Enabled): As a user with web search enabled, ask a current events question — confirm web results are integrated and properly attributed; Regulated User Exclusion: As a registered representative or trading desk user, verify web search is not available in Copilot; SharePoint Agent Configuration: Verify default web search setting for new SharePoint agents is "disabled"; Audit Trail: Confirm web search usage events are captured in audit logs; Decision Documentation: Verify that a documented risk assessment and approval record exists for the web search configuration; Review Cadence: Confirm quarterly (Baseline/Recommended) or annual (Regulated) review of web search policy is scheduled; Vendor Risk Assessment: Verify that Bing/web search data processing is included in the firm's third-party vendor risk assessment (if web search is enabled for any users)</t>
+          <t>Microsoft 365 admin center Web Content setting screenshot; Approved user group list for web search enablement; DLP policy evidence showing SIT-based web-search restriction; Audit log review cadence for web-search usage</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Tenant Geography Documented: Verify that the tenant's primary data location is documented and accessible to compliance; Copilot Processing Location: Confirm that Copilot processing occurs within the tenant's provisioned geography (verify via Microsoft documentation or support confirmation); ADR Status: Verify ADR subscription status if contractual residency assurances are required; Multi-Geo Configuration: For multinational firms, verify that users in each jurisdiction are assigned the correct preferred data location; Data Flow Mapping: Confirm a Copilot data flow map exists that documents source, processing, output, and ancillary data locations; Privacy Impact Assessment: Verify that Copilot is included in the firm's DPIA or privacy impact assessment (required for firms subject to GDPR or state privacy laws); Cross-Border Transfer Mechanisms: If data crosses borders, verify that appropriate transfer mechanisms (SCCs, DPF certification) are in place; Vendor Risk Assessment: Confirm that Copilot data residency is documented in the firm's vendor risk assessment for Microsoft; Review Cadence: Verify that data residency review is scheduled at the appropriate frequency (annually for Baseline, quarterly for Recommended, real-time for Regulated); Regulatory Examination Package: Confirm that data residency documentation is included in the firm's regulatory examination readiness materials</t>
+          <t>Data residency policy aligned to Copilot processing locations; Multi-geo configuration verification for Copilot workloads; Cross-border data flow map and approval records; Data sovereignty compliance documentation</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>MDCA Connectivity: Verify that Microsoft 365 apps are connected to Defender for Cloud Apps and showing activity data; Conditional Access App Control: Confirm at least one Conditional Access policy routes Copilot sessions through MDCA App Control; Session Policy Active: Verify that session monitoring policies for Copilot are enabled and generating logs; Anomaly Detection: Confirm built-in anomaly detection policies are enabled and tuned for the organization's user population; Alert Generation: Trigger a test alert (e.g., access Copilot from an unusual location) and confirm the alert appears in MDCA; Alert Routing: Verify that high-severity MDCA alerts are routed to the appropriate team (security, compliance) within the defined SLA; SIEM Integration: Confirm MDCA alerts and activity logs are flowing to the firm's SIEM or Microsoft Sentinel; Activity Policy Testing: Submit a high volume of Copilot interactions in a test environment and confirm the activity policy triggers; Generative AI App Catalog: Navigate to Defender portal &gt; Cloud Apps &gt; Cloud app catalog &gt; filter by Generative AI category and confirm the catalog is accessible; confirm governance policies exist for high-risk generative AI apps; Agent Threat Detection: Confirm agent monitoring alerts are enabled in Defender XDR; verify at least one agent-related detection rule is configured for Copilot agent deployments; Investigation Workflow: Verify that documented procedures exist for investigating MDCA alerts and agent threat detection alerts related to Copilot usage; Periodic Review: Confirm that MDCA policies are reviewed monthly (Recommended) or quarterly (Regulated) with documented results</t>
+          <t>Defender for Cloud Apps session policy configuration for Copilot; Anomaly detection alert rules targeting Copilot usage; Alert review cadence documentation; SOC integration evidence for Copilot-related alerts</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Third-Party Plugin Status: Verify that third-party plugins are disabled (Baseline) or restricted to approved plugins only (Recommended/Regulated); User Consent Blocked: Confirm that users cannot consent to OAuth applications — attempt user consent and verify it is blocked; Admin Consent Workflow: Verify that admin consent requests are routed to the security team and that a documented review process exists; Plugin Inventory: Confirm a current inventory of deployed plugins exists with publisher, permissions, and last review date; Graph Connector Governance: Verify that Graph connector deployment requires admin approval and that ingested data is classified; Plugin Approval Workflow: Confirm a documented plugin approval workflow exists with security, privacy, and compliance review steps; Permission Scoping: For approved plugins, verify that granted permissions follow the principle of least privilege; Plugin Usage Monitoring: Verify that plugin usage events are captured in audit logs and monitored; Third-Party Risk Assessment: Confirm that plugin publishers have been assessed under the firm's third-party risk management framework; Periodic Review: Confirm that approved plugins are re-assessed at least annually (Recommended) or quarterly (Regulated)</t>
+          <t>Plug-in and connector inventory with approval status; Risk classification for each approved connector; Data-flow assessment for connectors accessing regulated data; Documented review cadence and most recent review date</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>User access scoped: Verify agent access is limited to the approved users or groups.; Allowed types configured: Confirm allowed agent types match the institution's policy.; Sharing rules configured: Verify broad agent sharing is limited or approved.; Registry inventory current: Confirm published and shared agents are inventoried and owned.; SharePoint source review completed: Confirm high-risk agents have documented knowledge-source review.; Exception handling documented: Verify any external or high-risk agent exceptions have approval evidence.</t>
+          <t>Declarative agent inventory with owner and risk classification; Publishing-approval workflow documentation; Data-source scope documentation per agent; Most recent inventory review date</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Review federated connector status in M365 Admin Center — Connectors are disabled (Baseline) or restricted to approved connectors only; Verify no unauthorized connector authentications — Audit log shows no connector authentication events from unapproved user groups; Confirm connector inventory is documented — Current list of enabled connectors with vendor, data flow, and last review date; Test connector user scoping — Unapproved users cannot authenticate or invoke federated connectors; Verify third-party risk assessment exists — Each enabled connector vendor has a current risk assessment on file; Test DLP policy coverage for connector data — Connector-sourced data in Copilot responses triggers applicable DLP policies; Verify information barrier scope — Connector data flows respect information barrier boundaries; Review connector usage audit trail — Connector invocation events appear in Purview audit log with required detail; Confirm examination-ready documentation — Connector inventory, risk assessments, and usage reports are packaged for examination; Run quarterly connector re-assessment — All enabled connectors have been re-assessed within the last quarter</t>
+          <t>Federated connector and MCP endpoint allow-list; Approval workflow documentation; Data-flow assessment per endpoint; Review cadence and most recent review date</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Review incident classification taxonomy — AI-specific incident types documented and current; Verify incident reporting channel is operational — Reporting channel accessible to all Copilot users; Confirm escalation paths are documented and tested — Escalation contacts current and reachable; Review incident log for the past quarter — All Copilot incidents logged with classification and resolution; Verify root cause analysis completion for S1/S2 incidents — RCA completed within 30 days for all S1/S2 incidents; Confirm regulatory notification mapping is current — Notification requirements documented and reviewed in past 12 months; Review remediation tracking for open items — All remediation items tracked with target dates and owners; Verify tabletop exercise completion (Regulated) — Exercise completed within past 12 months with documented findings</t>
+          <t>Incident-response runbook covering Copilot-specific scenarios; Severity classification scheme for Copilot incidents; Reporting path documentation (internal + regulatory if required); Root-cause-analysis template and recent RCA examples</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Review Copilot dependency assessment — Assessment completed and current within past 12 months; Verify fallback procedures exist for High-dependency workflows — Documented procedures available and accessible to affected teams; Confirm Service Health monitoring is configured — Email alerts active for Copilot-related services; Review BCP for Copilot inclusion — Copilot addressed in technology dependency section of BCP; Verify fallback procedure testing results — Testing completed within past 12 months with documented results; Confirm communication plan templates are current — Templates updated and distribution lists current; Review Microsoft SLA documentation — SLA terms documented and service credit process understood; Verify critical regulatory functions are not solely Copilot-dependent — Regulatory reporting and filing processes have manual alternatives</t>
+          <t>BC/DR plan covering Copilot-dependent workflows; Fallback procedure documentation for Copilot outages; Most recent BC/DR test results (within 12 months); Copilot dependency assessment for critical business processes</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
@@ -910,7 +910,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Verify Sentinel data connectors are active and ingesting Copilot events — Data flowing from Microsoft 365, Entra ID, and Purview connectors; Run sample KQL query against Copilot events — Query returns results, confirming event capture; Review analytics rules for Copilot detections — At least 3 active analytics rules targeting Copilot events; Verify alert notification routing — Alerts route to SOC or designated security team; Review Copilot security workbook — Workbook displays current data with all panels populated; Test SOAR playbook execution (Recommended) — Playbook executes correctly on test incident; Confirm log retention settings — Retention meets regulatory requirements; Verify SOC coverage of Copilot alerts — SOC runbook includes Copilot alert triage procedures</t>
+          <t>Sentinel analytic rules targeting Copilot scenarios; Rule tuning cadence and most recent tuning date; SOC integration documentation for Copilot alerts; Recent alert log showing Copilot detection rule activity</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>

--- a/assessment/templates/security-admin-checklist.xlsx
+++ b/assessment/templates/security-admin-checklist.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Security Admin'!$A$4:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Security Admin'!$A$4:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Security Admin  |  FSI Copilot Governance Framework v1.4  |  9 controls</t>
+          <t>Role: Security Admin  |  FSI Copilot Governance Framework v1.8  |  10 controls</t>
         </is>
       </c>
     </row>
@@ -916,14 +916,53 @@
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
     </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Microsoft Scout Governance</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>P4 – Operations &amp; Lifecycle</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Baseline / Recommended / Regulated</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Copilot admin center; Teams/Viva; Sentinel</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Is Microsoft Scout governed across Frontier scope, endpoint policy plus attestation, and GitHub Copilot entitlement with documented supervision and boundary risk controls before enablement?</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I13"/>
+  <autoFilter ref="A4:I14"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
+    <dataValidation sqref="H5:H14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/assessment/templates/security-admin-checklist.xlsx
+++ b/assessment/templates/security-admin-checklist.xlsx
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Security Admin  |  FSI Copilot Governance Framework v1.8  |  10 controls</t>
+          <t>Role: Security Admin  |  FSI Copilot Governance Framework v1.8.0  |  10 controls</t>
         </is>
       </c>
     </row>

--- a/assessment/templates/security-admin-checklist.xlsx
+++ b/assessment/templates/security-admin-checklist.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Security Admin'!$A$4:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Security Admin'!$A$4:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Security Admin  |  FSI Copilot Governance Framework v1.4  |  9 controls</t>
+          <t>Role: Security Admin  |  FSI Copilot Governance Framework v1.8.0  |  10 controls</t>
         </is>
       </c>
     </row>
@@ -916,14 +916,53 @@
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
     </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Microsoft Scout Governance</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>P4 – Operations &amp; Lifecycle</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Baseline / Recommended / Regulated</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Copilot admin center; Teams/Viva; Sentinel</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Is Microsoft Scout governed across Frontier scope, endpoint policy plus attestation, and GitHub Copilot entitlement with documented supervision and boundary risk controls before enablement?</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Frontier enrollment and scoping record for tenant and pilot groups; Intune policy export showing Scout enablement profile assignment and effective state; Admin attestation record naming approver and completion date; GitHub Copilot Business/Enterprise entitlement export matched to pilot users; Documented default permission posture for local files, shell commands, and browser actions; Autonomous-mode and unattended-automation decision records with scope constraints; Approved MCP inventory including authentication, egress, and data-path classification; Boundary map showing M365-protected data vs GitHub/local/third-party processing surfaces; Known unsupported evidence register (local automation artifacts, local MCP output, third-party inference telemetry)</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I13"/>
+  <autoFilter ref="A4:I14"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
+    <dataValidation sqref="H5:H14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Select Yes, Partial, or No" promptTitle="Status" prompt="Select response" type="list">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/assessment/templates/security-admin-checklist.xlsx
+++ b/assessment/templates/security-admin-checklist.xlsx
@@ -910,7 +910,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Sentinel analytic rules targeting Copilot scenarios; Rule tuning cadence and most recent tuning date; SOC integration documentation for Copilot alerts; Recent alert log showing Copilot detection rule activity</t>
+          <t>Sentinel analytic rules targeting Copilot scenarios; Rule tuning cadence and most recent tuning date; SOC integration documentation for Copilot alerts; Recent alert log showing Copilot detection rule activity; Collector output showing CopilotActivity query status for RecordType CopilotInteraction (records_found / no_records / unavailable / query failure)</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>

--- a/assessment/templates/security-admin-checklist.xlsx
+++ b/assessment/templates/security-admin-checklist.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Copilot Web Search and Web Grounding Controls</t>
+          <t>Is the Copilot web search setting configured to the approved tenant posture and reviewed on a documented cadence?</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Data Residency and Cross-Border Data Flow Governance</t>
+          <t>Are Copilot data residency commitments (Advanced Data Residency and EU Data Boundary scope) documented and reconciled against the tenant configuration?</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">

--- a/assessment/templates/security-admin-checklist.xlsx
+++ b/assessment/templates/security-admin-checklist.xlsx
@@ -593,12 +593,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Copilot Web Search and Web Grounding Controls</t>
+          <t>Is the Copilot web search setting configured to the approved tenant posture and reviewed on a documented cadence?</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Microsoft 365 admin center Web Content setting screenshot; Approved user group list for web search enablement; DLP policy evidence showing SIT-based web-search restriction; Audit log review cadence for web-search usage</t>
+          <t>Cloud Policy configuration screenshot for 'Allow web search in Copilot'; Approved user group list for web search enablement; DLP policy evidence showing SIT-based web-search restriction; Audit log review cadence for web-search usage</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
@@ -632,7 +632,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Data Residency and Cross-Border Data Flow Governance</t>
+          <t>Are Copilot data residency commitments (Advanced Data Residency and EU Data Boundary scope) documented and reconciled against the tenant configuration?</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Is the plug-in / connector inventory reviewed and approved on a documented cadence, with un-approved connectors blocked?</t>
+          <t>Are the Agent Registry, Agent Tools, Copilot connectors, consent controls, and plugin audit evidence reconciled to approved inventory on a documented cadence?</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Plug-in and connector inventory with approval status; Risk classification for each approved connector; Data-flow assessment for connectors accessing regulated data; Documented review cadence and most recent review date</t>
+          <t>Agent Registry export with owner, availability, and approval status; Agent Tools registry, plugin, and request export with user/group scope; Copilot connector inventory with authentication, ACL, schema, sync, and risk review; Entra user-consent policy, admin-consent workflow, and existing-grant review; Paged 30-day accepted and rejected plugin-usage exports, allow-lists, and segment settings; Documented review cadence, decisions, and most recent review date</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>

--- a/assessment/templates/security-admin-checklist.xlsx
+++ b/assessment/templates/security-admin-checklist.xlsx
@@ -793,7 +793,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Federated connector and MCP endpoint allow-list; Approval workflow documentation; Data-flow assessment per endpoint; Review cadence and most recent review date</t>
+          <t>Federated connector and MCP endpoint allow-list; Allowed agent types publisher-category settings; Connector allowed-user and staged-rollout settings; Controlled approved and unapproved user access test; Approval workflow documentation; Data-flow assessment per endpoint; Review cadence and most recent review date</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>

--- a/assessment/templates/security-admin-checklist.xlsx
+++ b/assessment/templates/security-admin-checklist.xlsx
@@ -793,7 +793,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Federated connector and MCP endpoint allow-list; Allowed agent types publisher-category settings; Connector allowed-user and staged-rollout settings; Controlled approved and unapproved user access test; Approval workflow documentation; Data-flow assessment per endpoint; Review cadence and most recent review date</t>
+          <t>Federated connector and MCP endpoint allow-list; Allowed agent types publisher-category settings; Connector allowed-user and staged-rollout settings; Controlled approved and unapproved user access test; User-scoped authentication and source-permission evidence; Approval workflow documentation; Data-flow assessment per endpoint; Review cadence and most recent review date</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>

--- a/assessment/templates/security-admin-checklist.xlsx
+++ b/assessment/templates/security-admin-checklist.xlsx
@@ -793,7 +793,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Federated connector and MCP endpoint allow-list; Approval workflow documentation; Data-flow assessment per endpoint; Review cadence and most recent review date</t>
+          <t>Federated connector and MCP endpoint allow-list; Allowed agent types publisher-category settings; Connector allowed-user and staged-rollout settings; Controlled approved and unapproved user access test; User-scoped authentication and source-permission evidence; Approval workflow documentation; Data-flow assessment per endpoint; Review cadence and most recent review date</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
